--- a/app1/Excelfiles/July10000mummy.xlsx
+++ b/app1/Excelfiles/July10000mummy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,13 +1489,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="F41" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
